--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -835,7 +835,7 @@
     <t>0.0301,0.7524,0.0001,0.0113</t>
   </si>
   <si>
-    <t>0.0973,0.4617,0.0010,0.1018</t>
+    <t>0.0973,0.4618,0.0010,0.1018</t>
   </si>
   <si>
     <t>0.9026,0.2653,0.0001,0.0000</t>
@@ -1183,7 +1183,7 @@
     <t>0.9108,0.1829,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.4591,0.7301,0.0000,0.0000</t>
+    <t>0.4591,0.7302,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.5977,0.5751,0.0001,0.0000</t>
@@ -1261,7 +1261,7 @@
     <t>0.0025,0.0000,0.9994,0.0000</t>
   </si>
   <si>
-    <t>0.1992,0.0001,0.9289,0.0000</t>
+    <t>0.1993,0.0001,0.9289,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0038</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
   <si>
     <t>Filename</t>
   </si>
@@ -814,9 +814,15 @@
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>1,0,0,0</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,0</t>
   </si>
   <si>
@@ -826,55 +832,55 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.1594,0.6666,0.0120,0.0201</t>
-  </si>
-  <si>
-    <t>0.0058,0.3875,0.0004,0.8204</t>
-  </si>
-  <si>
-    <t>0.0301,0.7524,0.0001,0.0113</t>
-  </si>
-  <si>
-    <t>0.0973,0.4618,0.0010,0.1018</t>
-  </si>
-  <si>
-    <t>0.9026,0.2653,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6190,0.6951,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8134,0.4118,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9631,0.0877,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0826,0.9718,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.3169,0.8749,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9215,0.2028,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8674,0.3541,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0339,0.9403,0.0220,0.0114</t>
-  </si>
-  <si>
-    <t>0.0165,0.9288,0.0788,0.0083</t>
-  </si>
-  <si>
-    <t>0.1855,0.1697,0.3072,0.0053</t>
-  </si>
-  <si>
-    <t>0.0235,0.5161,0.2951,0.0109</t>
-  </si>
-  <si>
-    <t>0.4902,0.1659,0.1333,0.0010</t>
+    <t>0.1593,0.6671,0.0120,0.0201</t>
+  </si>
+  <si>
+    <t>0.0058,0.3883,0.0004,0.8200</t>
+  </si>
+  <si>
+    <t>0.0300,0.7529,0.0001,0.0113</t>
+  </si>
+  <si>
+    <t>0.0972,0.4624,0.0010,0.1016</t>
+  </si>
+  <si>
+    <t>0.9025,0.2656,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6185,0.6956,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8131,0.4124,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9631,0.0878,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0824,0.9718,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3166,0.8751,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9214,0.2032,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8671,0.3546,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0338,0.9405,0.0220,0.0114</t>
+  </si>
+  <si>
+    <t>0.0165,0.9289,0.0787,0.0083</t>
+  </si>
+  <si>
+    <t>0.1853,0.1701,0.3069,0.0053</t>
+  </si>
+  <si>
+    <t>0.0235,0.5167,0.2949,0.0109</t>
+  </si>
+  <si>
+    <t>0.4898,0.1662,0.1333,0.0010</t>
   </si>
   <si>
     <t>0.0001,1.0000,0.0001,0.0000</t>
@@ -889,19 +895,19 @@
     <t>0.0003,0.9998,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0643,0.1157,0.4650,0.0370</t>
-  </si>
-  <si>
-    <t>0.0172,0.3729,0.3665,0.0372</t>
-  </si>
-  <si>
-    <t>0.0693,0.0226,0.8476,0.0044</t>
-  </si>
-  <si>
-    <t>0.0185,0.1179,0.7351,0.0205</t>
-  </si>
-  <si>
-    <t>0.0491,0.0529,0.8181,0.0095</t>
+    <t>0.0643,0.1160,0.4647,0.0370</t>
+  </si>
+  <si>
+    <t>0.0172,0.3735,0.3664,0.0372</t>
+  </si>
+  <si>
+    <t>0.0693,0.0226,0.8474,0.0044</t>
+  </si>
+  <si>
+    <t>0.0185,0.1182,0.7349,0.0205</t>
+  </si>
+  <si>
+    <t>0.0491,0.0530,0.8180,0.0095</t>
   </si>
   <si>
     <t>0.0370,0.0061,0.9312,0.0122</t>
@@ -916,16 +922,16 @@
     <t>0.0361,0.9818,0.0004,0.0001</t>
   </si>
   <si>
-    <t>0.0495,0.0331,0.8269,0.0023</t>
-  </si>
-  <si>
-    <t>0.0166,0.9814,0.0098,0.0006</t>
-  </si>
-  <si>
-    <t>0.6375,0.5058,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.1231,0.9307,0.0035,0.0001</t>
+    <t>0.0495,0.0332,0.8266,0.0023</t>
+  </si>
+  <si>
+    <t>0.0165,0.9815,0.0098,0.0006</t>
+  </si>
+  <si>
+    <t>0.6371,0.5063,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.1230,0.9307,0.0035,0.0001</t>
   </si>
   <si>
     <t>0.0044,0.9985,0.0003,0.0000</t>
@@ -934,19 +940,19 @@
     <t>0.0126,0.9927,0.0056,0.0000</t>
   </si>
   <si>
-    <t>0.0008,0.9513,0.7329,0.0002</t>
+    <t>0.0008,0.9514,0.7329,0.0002</t>
   </si>
   <si>
     <t>0.0012,0.0021,0.9941,0.0031</t>
   </si>
   <si>
-    <t>0.0057,0.0561,0.9367,0.0074</t>
-  </si>
-  <si>
-    <t>0.0105,0.0147,0.8204,0.0389</t>
-  </si>
-  <si>
-    <t>0.0008,0.9260,0.6755,0.0013</t>
+    <t>0.0057,0.0563,0.9367,0.0074</t>
+  </si>
+  <si>
+    <t>0.0105,0.0148,0.8203,0.0389</t>
+  </si>
+  <si>
+    <t>0.0008,0.9261,0.6753,0.0013</t>
   </si>
   <si>
     <t>0.0011,0.9985,0.0031,0.0000</t>
@@ -955,7 +961,7 @@
     <t>0.0013,0.0056,0.9847,0.0061</t>
   </si>
   <si>
-    <t>0.0001,0.9987,0.0002,0.0341</t>
+    <t>0.0001,0.9987,0.0002,0.0340</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
@@ -970,7 +976,7 @@
     <t>0.0001,0.0035,0.9971,0.0010</t>
   </si>
   <si>
-    <t>0.0005,0.4463,0.8660,0.0075</t>
+    <t>0.0005,0.4468,0.8661,0.0075</t>
   </si>
   <si>
     <t>0.0076,0.0032,0.9703,0.0172</t>
@@ -982,31 +988,31 @@
     <t>0.0143,0.0142,0.9639,0.0044</t>
   </si>
   <si>
-    <t>0.0063,0.5659,0.2420,0.0477</t>
-  </si>
-  <si>
-    <t>0.2286,0.9155,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.8958,0.1500,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.5244,0.7430,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7242,0.1648,0.0177,0.0001</t>
-  </si>
-  <si>
-    <t>0.9437,0.0787,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9069,0.1601,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9318,0.1354,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9987,0.3041,0.0001</t>
+    <t>0.0063,0.5665,0.2419,0.0476</t>
+  </si>
+  <si>
+    <t>0.2282,0.9157,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.8957,0.1503,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.5239,0.7434,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7239,0.1652,0.0177,0.0001</t>
+  </si>
+  <si>
+    <t>0.9437,0.0789,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9068,0.1604,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9317,0.1356,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9987,0.3042,0.0001</t>
   </si>
   <si>
     <t>0.0003,0.0055,0.9973,0.0007</t>
@@ -1015,7 +1021,7 @@
     <t>0.0003,0.0041,0.9874,0.0074</t>
   </si>
   <si>
-    <t>0.0004,0.9945,0.2535,0.0004</t>
+    <t>0.0004,0.9945,0.2538,0.0004</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9996,0.0006</t>
@@ -1024,121 +1030,121 @@
     <t>0.0009,0.9995,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.7629,0.2594,0.0095,0.0001</t>
+    <t>0.7627,0.2598,0.0095,0.0001</t>
   </si>
   <si>
     <t>0.0360,0.9609,0.0219,0.0015</t>
   </si>
   <si>
-    <t>0.0971,0.4940,0.2181,0.0044</t>
-  </si>
-  <si>
-    <t>0.0008,0.9902,0.2861,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.9531,0.7883,0.0003</t>
+    <t>0.0970,0.4945,0.2178,0.0044</t>
+  </si>
+  <si>
+    <t>0.0008,0.9902,0.2863,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.9531,0.7884,0.0003</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0126,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.9723,0.5940,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.5483,0.0004,0.9824</t>
-  </si>
-  <si>
-    <t>0.0014,0.3229,0.0005,0.9816</t>
-  </si>
-  <si>
-    <t>0.0016,0.0333,0.0009,0.9973</t>
-  </si>
-  <si>
-    <t>0.0006,0.1826,0.0005,0.9934</t>
-  </si>
-  <si>
-    <t>0.0018,0.5281,0.0004,0.8385</t>
-  </si>
-  <si>
-    <t>0.0004,0.1220,0.0010,0.9980</t>
-  </si>
-  <si>
-    <t>0.0003,0.9984,0.1260,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.7407,0.9709,0.0003</t>
+    <t>0.0004,0.9723,0.5942,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.5491,0.0004,0.9823</t>
+  </si>
+  <si>
+    <t>0.0014,0.3236,0.0005,0.9816</t>
+  </si>
+  <si>
+    <t>0.0016,0.0334,0.0009,0.9973</t>
+  </si>
+  <si>
+    <t>0.0006,0.1833,0.0005,0.9934</t>
+  </si>
+  <si>
+    <t>0.0018,0.5289,0.0004,0.8380</t>
+  </si>
+  <si>
+    <t>0.0004,0.1225,0.0010,0.9980</t>
+  </si>
+  <si>
+    <t>0.0003,0.9984,0.1261,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.7409,0.9709,0.0003</t>
   </si>
   <si>
     <t>0.0009,0.9970,0.0232,0.0005</t>
   </si>
   <si>
-    <t>0.0004,0.8701,0.9367,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9976,0.3963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0195,0.0002</t>
-  </si>
-  <si>
-    <t>0.4300,0.8211,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.3135,0.8876,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2506,0.8805,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2817,0.8873,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8264,0.4395,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9191,0.1454,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8754,0.2519,0.0006,0.0000</t>
+    <t>0.0004,0.8702,0.9367,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9976,0.3964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9988,0.0194,0.0002</t>
+  </si>
+  <si>
+    <t>0.4293,0.8216,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3130,0.8878,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2503,0.8807,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2813,0.8876,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8261,0.4400,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9190,0.1456,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8752,0.2523,0.0006,0.0000</t>
   </si>
   <si>
     <t>0.9697,0.0169,0.0023,0.0009</t>
   </si>
   <si>
-    <t>0.9492,0.1211,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7362,0.4866,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8368,0.3795,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8464,0.3157,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6711,0.5815,0.0001,0.0000</t>
+    <t>0.9491,0.1213,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7359,0.4870,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8365,0.3800,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8462,0.3161,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6706,0.5821,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9817,0.0333,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.7450,0.4687,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9444,0.1341,0.0002,0.0000</t>
+    <t>0.7448,0.4690,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9443,0.1343,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0012,0.0002,0.9986,0.0003</t>
   </si>
   <si>
-    <t>0.0500,0.2949,0.4795,0.0049</t>
-  </si>
-  <si>
-    <t>0.3335,0.0832,0.3305,0.0132</t>
-  </si>
-  <si>
-    <t>0.0353,0.1779,0.5860,0.0085</t>
+    <t>0.0500,0.2951,0.4794,0.0049</t>
+  </si>
+  <si>
+    <t>0.3332,0.0834,0.3303,0.0132</t>
+  </si>
+  <si>
+    <t>0.0353,0.1781,0.5860,0.0085</t>
   </si>
   <si>
     <t>0.0008,0.9997,0.0001,0.0000</t>
@@ -1150,19 +1156,19 @@
     <t>0.0066,0.9972,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.0205,0.9585,0.0234,0.0052</t>
-  </si>
-  <si>
-    <t>0.0135,0.7907,0.1473,0.0259</t>
-  </si>
-  <si>
-    <t>0.0452,0.8972,0.0392,0.0044</t>
-  </si>
-  <si>
-    <t>0.0195,0.9514,0.0330,0.0176</t>
-  </si>
-  <si>
-    <t>0.0012,0.9536,0.0360,0.3111</t>
+    <t>0.0205,0.9586,0.0234,0.0052</t>
+  </si>
+  <si>
+    <t>0.0135,0.7910,0.1473,0.0259</t>
+  </si>
+  <si>
+    <t>0.0452,0.8973,0.0392,0.0044</t>
+  </si>
+  <si>
+    <t>0.0195,0.9515,0.0330,0.0175</t>
+  </si>
+  <si>
+    <t>0.0012,0.9536,0.0360,0.3105</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
@@ -1180,43 +1186,43 @@
     <t>0.0022,0.9987,0.0008,0.0000</t>
   </si>
   <si>
-    <t>0.9108,0.1829,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.4591,0.7302,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5977,0.5751,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8407,0.2841,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8922,0.1051,0.0018,0.0007</t>
-  </si>
-  <si>
-    <t>0.9338,0.1378,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8964,0.2193,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9415,0.1172,0.0004,0.0000</t>
+    <t>0.9106,0.1832,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4588,0.7304,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5973,0.5756,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8406,0.2844,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8921,0.1054,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9336,0.1381,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.8962,0.2198,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9414,0.1174,0.0004,0.0000</t>
   </si>
   <si>
     <t>0.0010,0.9716,0.4340,0.0012</t>
   </si>
   <si>
-    <t>0.0012,0.8934,0.8628,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0557,0.9929,0.0005</t>
+    <t>0.0012,0.8936,0.8627,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0559,0.9929,0.0005</t>
   </si>
   <si>
     <t>0.0023,0.0122,0.9928,0.0006</t>
   </si>
   <si>
-    <t>0.2815,0.5080,0.0553,0.0039</t>
+    <t>0.2811,0.5086,0.0553,0.0039</t>
   </si>
   <si>
     <t>0.0078,0.9909,0.0033,0.0010</t>
@@ -1225,43 +1231,43 @@
     <t>0.0442,0.0024,0.9341,0.0159</t>
   </si>
   <si>
-    <t>0.0413,0.9269,0.0251,0.0065</t>
-  </si>
-  <si>
-    <t>0.0021,0.1179,0.0007,0.9839</t>
-  </si>
-  <si>
-    <t>0.0000,0.0126,0.0002,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0101,0.0005,0.9999</t>
-  </si>
-  <si>
-    <t>0.0008,0.2893,0.0004,0.9768</t>
+    <t>0.0413,0.9271,0.0251,0.0065</t>
+  </si>
+  <si>
+    <t>0.0021,0.1182,0.0007,0.9839</t>
+  </si>
+  <si>
+    <t>0.0000,0.0127,0.0002,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0102,0.0005,0.9999</t>
+  </si>
+  <si>
+    <t>0.0008,0.2901,0.0004,0.9768</t>
   </si>
   <si>
     <t>0.0005,0.9984,0.0486,0.0001</t>
   </si>
   <si>
-    <t>0.8069,0.2875,0.0014,0.0001</t>
+    <t>0.8066,0.2880,0.0014,0.0001</t>
   </si>
   <si>
     <t>0.0042,0.9979,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.8515,0.2350,0.0011,0.0000</t>
+    <t>0.8513,0.2353,0.0011,0.0000</t>
   </si>
   <si>
     <t>0.0060,0.9980,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.5628,0.5673,0.0002,0.0001</t>
+    <t>0.5622,0.5679,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.0025,0.0000,0.9994,0.0000</t>
   </si>
   <si>
-    <t>0.1993,0.0001,0.9289,0.0000</t>
+    <t>0.1991,0.0001,0.9289,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0038</t>
@@ -1270,49 +1276,49 @@
     <t>0.9693,0.0102,0.0038,0.0001</t>
   </si>
   <si>
-    <t>0.7640,0.5012,0.0001,0.0000</t>
+    <t>0.7636,0.5017,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0550,0.9677,0.0027,0.0001</t>
   </si>
   <si>
-    <t>0.4512,0.6360,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.1551,0.9303,0.0010,0.0000</t>
+    <t>0.4508,0.6366,0.0040,0.0003</t>
+  </si>
+  <si>
+    <t>0.1547,0.9305,0.0010,0.0000</t>
   </si>
   <si>
     <t>0.0011,0.9990,0.0007,0.0002</t>
   </si>
   <si>
-    <t>0.0204,0.9868,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.2361,0.8029,0.0155,0.0009</t>
-  </si>
-  <si>
-    <t>0.3526,0.8514,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3111,0.8417,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6630,0.5592,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9253,0.1366,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.4444,0.8047,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2086,0.9069,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4779,0.7509,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8429,0.3088,0.0003,0.0000</t>
+    <t>0.0204,0.9869,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.2357,0.8033,0.0155,0.0009</t>
+  </si>
+  <si>
+    <t>0.3520,0.8518,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3107,0.8420,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6625,0.5599,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9253,0.1368,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.4439,0.8051,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2083,0.9071,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4772,0.7515,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8426,0.3094,0.0003,0.0000</t>
   </si>
   <si>
     <t>0.0033,0.9982,0.0007,0.0000</t>
@@ -1321,40 +1327,40 @@
     <t>0.0045,0.9986,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0398,0.9897,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2554,0.8914,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.7402,0.5448,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.1175,0.9520,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9059,0.1559,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0599,0.9734,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.1940,0.4326,0.1492,0.0004</t>
-  </si>
-  <si>
-    <t>0.0964,0.9641,0.0010,0.0000</t>
+    <t>0.0397,0.9897,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.2551,0.8917,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.7398,0.5455,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1173,0.9521,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9057,0.1562,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0598,0.9734,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.1940,0.4329,0.1491,0.0004</t>
+  </si>
+  <si>
+    <t>0.0963,0.9642,0.0010,0.0000</t>
   </si>
   <si>
     <t>0.0044,0.0021,0.9936,0.0013</t>
   </si>
   <si>
-    <t>0.0007,0.1329,0.9405,0.0071</t>
-  </si>
-  <si>
-    <t>0.0473,0.0819,0.8266,0.0049</t>
-  </si>
-  <si>
-    <t>0.0032,0.6160,0.7375,0.0011</t>
+    <t>0.0007,0.1332,0.9405,0.0071</t>
+  </si>
+  <si>
+    <t>0.0473,0.0820,0.8266,0.0049</t>
+  </si>
+  <si>
+    <t>0.0032,0.6168,0.7372,0.0011</t>
   </si>
   <si>
     <t>0.0074,0.0221,0.9837,0.0012</t>
@@ -1363,34 +1369,34 @@
     <t>0.0017,0.0004,0.9974,0.0007</t>
   </si>
   <si>
-    <t>0.1231,0.2284,0.4098,0.0041</t>
-  </si>
-  <si>
-    <t>0.0528,0.8285,0.0696,0.0050</t>
-  </si>
-  <si>
-    <t>0.1069,0.0409,0.6421,0.0134</t>
-  </si>
-  <si>
-    <t>0.0144,0.9786,0.0130,0.0031</t>
+    <t>0.1230,0.2288,0.4095,0.0041</t>
+  </si>
+  <si>
+    <t>0.0528,0.8288,0.0696,0.0050</t>
+  </si>
+  <si>
+    <t>0.1068,0.0410,0.6419,0.0134</t>
+  </si>
+  <si>
+    <t>0.0144,0.9786,0.0129,0.0031</t>
   </si>
   <si>
     <t>0.0174,0.9544,0.0327,0.0082</t>
   </si>
   <si>
-    <t>0.0340,0.8897,0.0652,0.0020</t>
-  </si>
-  <si>
-    <t>0.1138,0.2653,0.2797,0.0083</t>
-  </si>
-  <si>
-    <t>0.0619,0.6353,0.1703,0.0086</t>
-  </si>
-  <si>
-    <t>0.0132,0.9818,0.0123,0.0022</t>
-  </si>
-  <si>
-    <t>0.0067,0.9981,0.0002,0.0000</t>
+    <t>0.0340,0.8898,0.0652,0.0020</t>
+  </si>
+  <si>
+    <t>0.1138,0.2657,0.2796,0.0083</t>
+  </si>
+  <si>
+    <t>0.0619,0.6358,0.1701,0.0085</t>
+  </si>
+  <si>
+    <t>0.0132,0.9819,0.0123,0.0022</t>
+  </si>
+  <si>
+    <t>0.0066,0.9981,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0028,0.9995,0.0000,0.0000</t>
@@ -1399,73 +1405,73 @@
     <t>0.0105,0.9974,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.7981,0.5084,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.1095,0.9729,0.0002,0.0000</t>
+    <t>0.7977,0.5092,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1093,0.9729,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0012,0.9990,0.0005,0.0001</t>
   </si>
   <si>
-    <t>0.3031,0.6693,0.0117,0.0017</t>
-  </si>
-  <si>
-    <t>0.0086,0.9606,0.0284,0.0422</t>
-  </si>
-  <si>
-    <t>0.0405,0.0333,0.4896,0.0810</t>
-  </si>
-  <si>
-    <t>0.0734,0.9023,0.0128,0.0032</t>
-  </si>
-  <si>
-    <t>0.0244,0.0110,0.9482,0.0068</t>
-  </si>
-  <si>
-    <t>0.0114,0.0270,0.9704,0.0014</t>
-  </si>
-  <si>
-    <t>0.0056,0.6540,0.4805,0.0015</t>
+    <t>0.3026,0.6698,0.0117,0.0017</t>
+  </si>
+  <si>
+    <t>0.0086,0.9607,0.0284,0.0422</t>
+  </si>
+  <si>
+    <t>0.0405,0.0333,0.4896,0.0808</t>
+  </si>
+  <si>
+    <t>0.0733,0.9025,0.0128,0.0032</t>
+  </si>
+  <si>
+    <t>0.0244,0.0110,0.9481,0.0068</t>
+  </si>
+  <si>
+    <t>0.0114,0.0271,0.9704,0.0014</t>
+  </si>
+  <si>
+    <t>0.0056,0.6546,0.4804,0.0015</t>
   </si>
   <si>
     <t>0.0029,0.0054,0.9925,0.0010</t>
   </si>
   <si>
-    <t>0.0087,0.3395,0.7147,0.0005</t>
-  </si>
-  <si>
-    <t>0.9366,0.1238,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.2394,0.9187,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0812,0.9693,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2460,0.8836,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1824,0.9302,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.4061,0.8359,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4532,0.8050,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9383,0.1135,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.2599,0.2953,0.1652,0.0019</t>
-  </si>
-  <si>
-    <t>0.0823,0.8739,0.0279,0.0008</t>
-  </si>
-  <si>
-    <t>0.2706,0.5382,0.0579,0.0047</t>
+    <t>0.0087,0.3399,0.7146,0.0005</t>
+  </si>
+  <si>
+    <t>0.9365,0.1240,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.2390,0.9189,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0810,0.9694,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2457,0.8838,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1822,0.9303,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4055,0.8363,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4527,0.8054,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9383,0.1137,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.2597,0.2957,0.1650,0.0019</t>
+  </si>
+  <si>
+    <t>0.0822,0.8742,0.0278,0.0008</t>
+  </si>
+  <si>
+    <t>0.2704,0.5386,0.0578,0.0047</t>
   </si>
   <si>
     <t>0.0009,0.0003,0.9984,0.0004</t>
@@ -1474,13 +1480,13 @@
     <t>0.0003,0.0014,0.9974,0.0012</t>
   </si>
   <si>
-    <t>0.0111,0.8465,0.2923,0.0070</t>
+    <t>0.0111,0.8468,0.2919,0.0070</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9998,0.0001</t>
   </si>
   <si>
-    <t>0.0225,0.6519,0.3657,0.0094</t>
+    <t>0.0225,0.6523,0.3655,0.0094</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
@@ -1489,43 +1495,43 @@
     <t>0.0023,0.0115,0.9794,0.0057</t>
   </si>
   <si>
-    <t>0.0124,0.9647,0.0381,0.0090</t>
-  </si>
-  <si>
-    <t>0.1641,0.4486,0.0816,0.0209</t>
-  </si>
-  <si>
-    <t>0.0936,0.1584,0.1309,0.0825</t>
-  </si>
-  <si>
-    <t>0.0837,0.9261,0.0040,0.0018</t>
-  </si>
-  <si>
-    <t>0.9234,0.2181,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.1235,0.9511,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5725,0.7666,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1811,0.9484,0.0001,0.0000</t>
+    <t>0.0123,0.9648,0.0380,0.0090</t>
+  </si>
+  <si>
+    <t>0.1639,0.4494,0.0815,0.0209</t>
+  </si>
+  <si>
+    <t>0.0935,0.1589,0.1308,0.0823</t>
+  </si>
+  <si>
+    <t>0.0836,0.9263,0.0040,0.0018</t>
+  </si>
+  <si>
+    <t>0.9233,0.2185,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1233,0.9511,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5720,0.7670,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1808,0.9485,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9754,0.0455,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.2228,0.9349,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4786,0.7551,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8441,0.3900,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.7083,0.6401,0.0044</t>
+    <t>0.2225,0.9350,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4781,0.7555,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8438,0.3905,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.7089,0.6399,0.0044</t>
   </si>
   <si>
     <t>0.0011,0.0048,0.9973,0.0002</t>
@@ -1534,37 +1540,37 @@
     <t>0.0015,0.0061,0.9963,0.0004</t>
   </si>
   <si>
-    <t>0.0237,0.9112,0.0810,0.0053</t>
-  </si>
-  <si>
-    <t>0.0098,0.0057,0.9779,0.0046</t>
-  </si>
-  <si>
-    <t>0.0399,0.9010,0.0105,0.0095</t>
-  </si>
-  <si>
-    <t>0.0273,0.8522,0.0610,0.0065</t>
+    <t>0.0237,0.9114,0.0809,0.0053</t>
+  </si>
+  <si>
+    <t>0.0098,0.0058,0.9779,0.0046</t>
+  </si>
+  <si>
+    <t>0.0398,0.9012,0.0105,0.0094</t>
+  </si>
+  <si>
+    <t>0.0273,0.8524,0.0610,0.0065</t>
   </si>
   <si>
     <t>0.0019,0.0006,0.9944,0.0031</t>
   </si>
   <si>
-    <t>0.4929,0.3578,0.0014,0.0042</t>
-  </si>
-  <si>
-    <t>0.0003,0.5457,0.0008,0.9938</t>
-  </si>
-  <si>
-    <t>0.0006,0.1855,0.0017,0.9949</t>
-  </si>
-  <si>
-    <t>0.0000,0.0049,0.0022,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0342,0.0004,0.9996</t>
-  </si>
-  <si>
-    <t>0.0425,0.6929,0.0073,0.1641</t>
+    <t>0.4928,0.3581,0.0014,0.0042</t>
+  </si>
+  <si>
+    <t>0.0003,0.5465,0.0008,0.9938</t>
+  </si>
+  <si>
+    <t>0.0006,0.1859,0.0017,0.9949</t>
+  </si>
+  <si>
+    <t>0.0000,0.0050,0.0022,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0343,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0425,0.6934,0.0073,0.1639</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1956,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1964,7 +1970,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1978,7 +1984,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1992,7 +1998,7 @@
         <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2003,10 +2009,10 @@
         <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2017,10 +2023,10 @@
         <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2031,10 +2037,10 @@
         <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2045,10 +2051,10 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2062,7 +2068,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2076,7 +2082,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2087,10 +2093,10 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2101,10 +2107,10 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2118,7 +2124,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2132,7 +2138,7 @@
         <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2146,7 +2152,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2160,7 +2166,7 @@
         <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2174,7 +2180,7 @@
         <v>266</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2188,7 +2194,7 @@
         <v>264</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2202,7 +2208,7 @@
         <v>264</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2216,7 +2222,7 @@
         <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2230,7 +2236,7 @@
         <v>264</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2244,7 +2250,7 @@
         <v>264</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2258,7 +2264,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2272,7 +2278,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2283,10 +2289,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2297,10 +2303,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2311,10 +2317,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2325,10 +2331,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2339,10 +2345,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2356,7 +2362,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,7 +2376,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2381,10 +2387,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2398,7 +2404,7 @@
         <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2409,10 +2415,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2426,7 +2432,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2440,7 +2446,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2454,7 +2460,7 @@
         <v>264</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2465,10 +2471,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2479,10 +2485,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2493,10 +2499,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2507,10 +2513,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2521,10 +2527,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2538,7 +2544,7 @@
         <v>264</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2549,10 +2555,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2566,7 +2572,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2580,7 +2586,7 @@
         <v>264</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2594,7 +2600,7 @@
         <v>264</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2608,7 +2614,7 @@
         <v>264</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2619,10 +2625,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2633,10 +2639,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2647,10 +2653,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2661,10 +2667,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2675,10 +2681,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2692,7 +2698,7 @@
         <v>264</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2706,7 +2712,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2717,10 +2723,10 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2731,10 +2737,10 @@
         <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2745,10 +2751,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2759,10 +2765,10 @@
         <v>259</v>
       </c>
       <c r="C60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2773,10 +2779,10 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2787,10 +2793,10 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2804,7 +2810,7 @@
         <v>264</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2815,10 +2821,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2829,10 +2835,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2846,7 +2852,7 @@
         <v>264</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2857,10 +2863,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2874,7 +2880,7 @@
         <v>264</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2888,7 +2894,7 @@
         <v>264</v>
       </c>
       <c r="D69" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2899,10 +2905,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D70" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2916,7 +2922,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2930,7 +2936,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2944,7 +2950,7 @@
         <v>264</v>
       </c>
       <c r="D73" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2955,10 +2961,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D74" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2972,7 +2978,7 @@
         <v>264</v>
       </c>
       <c r="D75" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2983,10 +2989,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D76" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2997,10 +3003,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D77" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3014,7 +3020,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3028,7 +3034,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3042,7 +3048,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3053,10 +3059,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D81" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3070,7 +3076,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3084,7 +3090,7 @@
         <v>264</v>
       </c>
       <c r="D83" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3095,10 +3101,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D84" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,7 +3118,7 @@
         <v>264</v>
       </c>
       <c r="D85" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3123,10 +3129,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D86" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3140,7 +3146,7 @@
         <v>264</v>
       </c>
       <c r="D87" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3154,7 +3160,7 @@
         <v>264</v>
       </c>
       <c r="D88" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3168,7 +3174,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3182,7 +3188,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3196,7 +3202,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3210,7 +3216,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3221,10 +3227,10 @@
         <v>259</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D93" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3235,10 +3241,10 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D94" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3249,10 +3255,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D95" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3263,10 +3269,10 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D96" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3277,10 +3283,10 @@
         <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D97" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3291,10 +3297,10 @@
         <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D98" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3305,10 +3311,10 @@
         <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D99" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3319,10 +3325,10 @@
         <v>259</v>
       </c>
       <c r="C100" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D100" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3333,10 +3339,10 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D101" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3347,10 +3353,10 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D102" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3361,10 +3367,10 @@
         <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D103" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3375,10 +3381,10 @@
         <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D104" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3389,10 +3395,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D105" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3406,7 +3412,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3420,7 +3426,7 @@
         <v>266</v>
       </c>
       <c r="D107" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3431,10 +3437,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D108" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3448,7 +3454,7 @@
         <v>264</v>
       </c>
       <c r="D109" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3462,7 +3468,7 @@
         <v>264</v>
       </c>
       <c r="D110" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3476,7 +3482,7 @@
         <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3490,7 +3496,7 @@
         <v>264</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3504,7 +3510,7 @@
         <v>264</v>
       </c>
       <c r="D113" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3518,7 +3524,7 @@
         <v>264</v>
       </c>
       <c r="D114" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3532,7 +3538,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3546,7 +3552,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3560,7 +3566,7 @@
         <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,7 +3580,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3588,7 +3594,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3602,7 +3608,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3616,7 +3622,7 @@
         <v>264</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3630,7 +3636,7 @@
         <v>264</v>
       </c>
       <c r="D122" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3644,7 +3650,7 @@
         <v>264</v>
       </c>
       <c r="D123" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3658,7 +3664,7 @@
         <v>264</v>
       </c>
       <c r="D124" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3672,7 +3678,7 @@
         <v>264</v>
       </c>
       <c r="D125" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3686,7 +3692,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3700,7 +3706,7 @@
         <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3711,10 +3717,10 @@
         <v>259</v>
       </c>
       <c r="C128" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D128" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3728,7 +3734,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3739,10 +3745,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D130" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3753,10 +3759,10 @@
         <v>259</v>
       </c>
       <c r="C131" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D131" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3767,10 +3773,10 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D132" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3781,10 +3787,10 @@
         <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D133" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3795,10 +3801,10 @@
         <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D134" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3809,10 +3815,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D135" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,7 +3832,7 @@
         <v>264</v>
       </c>
       <c r="D136" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3837,10 +3843,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D137" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3851,10 +3857,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D138" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3865,10 +3871,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D139" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3882,7 +3888,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3896,7 +3902,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3907,10 +3913,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3924,7 +3930,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3938,7 +3944,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3952,7 +3958,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3966,7 +3972,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3980,7 +3986,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3994,7 +4000,7 @@
         <v>264</v>
       </c>
       <c r="D148" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4005,10 +4011,10 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D149" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4022,7 +4028,7 @@
         <v>264</v>
       </c>
       <c r="D150" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4033,10 +4039,10 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D151" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4050,7 +4056,7 @@
         <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4061,10 +4067,10 @@
         <v>259</v>
       </c>
       <c r="C153" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D153" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4075,10 +4081,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D154" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4089,10 +4095,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D155" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4103,10 +4109,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D156" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4117,10 +4123,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D157" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4131,10 +4137,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D158" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4148,7 +4154,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4162,7 +4168,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4176,7 +4182,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4190,7 +4196,7 @@
         <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4204,7 +4210,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4218,7 +4224,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4232,7 +4238,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4246,7 +4252,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4257,10 +4263,10 @@
         <v>259</v>
       </c>
       <c r="C167" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D167" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4271,10 +4277,10 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D168" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4288,7 +4294,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4302,7 +4308,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4316,7 +4322,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4327,10 +4333,10 @@
         <v>259</v>
       </c>
       <c r="C172" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D172" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4344,7 +4350,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4358,7 +4364,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4372,7 +4378,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4386,7 +4392,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4397,10 +4403,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D177" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4414,7 +4420,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4425,10 +4431,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D179" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4442,7 +4448,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4456,7 +4462,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4470,7 +4476,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4481,10 +4487,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D183" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4495,10 +4501,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D184" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4509,10 +4515,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D185" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4523,10 +4529,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D186" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4537,10 +4543,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D187" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4551,10 +4557,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D188" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4568,7 +4574,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4582,7 +4588,7 @@
         <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4593,10 +4599,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D191" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4610,7 +4616,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4624,7 +4630,7 @@
         <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4638,7 +4644,7 @@
         <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4652,7 +4658,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,7 +4672,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,7 +4686,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4694,7 +4700,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4708,7 +4714,7 @@
         <v>264</v>
       </c>
       <c r="D199" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4722,7 +4728,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4733,10 +4739,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D201" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4750,7 +4756,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4764,7 +4770,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4778,7 +4784,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4792,7 +4798,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,7 +4812,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4820,7 +4826,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4831,10 +4837,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D208" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4845,10 +4851,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D209" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4862,7 +4868,7 @@
         <v>264</v>
       </c>
       <c r="D210" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4873,10 +4879,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D211" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4887,10 +4893,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D212" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4901,10 +4907,10 @@
         <v>259</v>
       </c>
       <c r="C213" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D213" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4918,7 +4924,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4932,7 +4938,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4946,7 +4952,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4960,7 +4966,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4974,7 +4980,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4988,7 +4994,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4999,10 +5005,10 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D220" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5016,7 +5022,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5030,7 +5036,7 @@
         <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5044,7 +5050,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5055,10 +5061,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D224" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5069,10 +5075,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D225" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5086,7 +5092,7 @@
         <v>264</v>
       </c>
       <c r="D226" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5097,10 +5103,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D227" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5114,7 +5120,7 @@
         <v>264</v>
       </c>
       <c r="D228" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5125,10 +5131,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D229" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5139,10 +5145,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D230" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5156,7 +5162,7 @@
         <v>264</v>
       </c>
       <c r="D231" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5170,7 +5176,7 @@
         <v>266</v>
       </c>
       <c r="D232" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5184,7 +5190,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5198,7 +5204,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5209,10 +5215,10 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D235" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5226,7 +5232,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5237,10 +5243,10 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D237" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5254,7 +5260,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5265,10 +5271,10 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D239" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5282,7 +5288,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5296,7 +5302,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5307,10 +5313,10 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D242" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5321,10 +5327,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D243" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5335,10 +5341,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D244" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5349,10 +5355,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D245" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5366,7 +5372,7 @@
         <v>264</v>
       </c>
       <c r="D246" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5377,10 +5383,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D247" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,7 +5400,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5408,7 +5414,7 @@
         <v>264</v>
       </c>
       <c r="D249" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5419,10 +5425,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D250" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5436,7 +5442,7 @@
         <v>266</v>
       </c>
       <c r="D251" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5447,10 +5453,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D252" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5464,7 +5470,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5478,7 +5484,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5492,7 +5498,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5506,7 +5512,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
